--- a/output/pdf_financials_xlsx/VO.xlsx
+++ b/output/pdf_financials_xlsx/VO.xlsx
@@ -1053,10 +1053,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000258</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.072759</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1071,31 +1071,31 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.006562</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.006613</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.007483</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.007483</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.020026</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.076514</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.062596</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.026964</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.082187</v>
       </c>
     </row>
     <row r="13">
@@ -2041,10 +2041,10 @@
         <v>-0.657369</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.365948</v>
+        <v>-1.366206</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.640096</v>
+        <v>-2.712855</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-3.524524</v>
@@ -2063,13 +2063,13 @@
         <v>-1.044018</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.33211</v>
+        <v>-0.338672</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.679272</v>
+        <v>-0.685885</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.658233</v>
+        <v>-1.665716</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -2077,19 +2077,19 @@
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-5.636732</v>
+        <v>-5.656758</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-18.325582</v>
+        <v>-18.402096</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>23.995543</v>
+        <v>23.932947</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.580479</v>
+        <v>-2.607443</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-3.549719</v>
+        <v>-3.631906</v>
       </c>
     </row>
     <row r="28">
@@ -2163,10 +2163,10 @@
         <v>-0.657369</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.347601</v>
+        <v>-1.347859</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.563873</v>
+        <v>-2.636632</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-3.358981</v>
@@ -2185,13 +2185,13 @@
         <v>-0.932051</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.245001</v>
+        <v>-0.251563</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.616554</v>
+        <v>-0.623167</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.608296</v>
+        <v>-1.615779</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -2199,19 +2199,19 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-5.598551</v>
+        <v>-5.618577</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-18.278432</v>
+        <v>-18.354946</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>24.035949</v>
+        <v>23.973353</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.562885</v>
+        <v>-2.589849</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-3.533934</v>
+        <v>-3.616121</v>
       </c>
     </row>
     <row r="30">
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.93635</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.170942</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>5.222744</v>
@@ -2514,19 +2514,19 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.516919</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.593793</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.209291</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.61354</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>1.086078</v>
       </c>
     </row>
     <row r="35">
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.18</v>
+        <v>1.11635</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.170942</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>5.222744</v>
@@ -2636,19 +2636,19 @@
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.516919</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.593793</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.209291</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>1.61354</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>1.086078</v>
       </c>
     </row>
     <row r="37">
@@ -3396,19 +3396,19 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.602417</v>
+        <v>0.085498</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.399485</v>
+        <v>0.805692</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.345309</v>
+        <v>0.136018</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>2.084699</v>
+        <v>0.471159</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.400858</v>
+        <v>0.31478</v>
       </c>
     </row>
     <row r="49">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -20595,7 +20595,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
@@ -74433,7 +74433,7 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
@@ -79976,7 +79976,7 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">

--- a/output/pdf_financials_xlsx/VO.xlsx
+++ b/output/pdf_financials_xlsx/VO.xlsx
@@ -1346,13 +1346,13 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.1239</v>
+        <v>-0.1239</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.1118</v>
+        <v>-0.1118</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.884428</v>
+        <v>-0.429687</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -2322,7 +2322,7 @@
         <v>-8.184791807594433</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-33.49984242997224</v>
+        <v>-16.27543089342206</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -4488,10 +4488,10 @@
         <v>0</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.487592</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.430713</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>0</v>
@@ -4677,16 +4677,16 @@
         <v>0</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.087034</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.5875</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.719592</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.6876100000000001</v>
       </c>
     </row>
     <row r="68">
@@ -6793,55 +6793,55 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.130783</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>-0.006059</v>
+        <v>0.034865</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0.032432</v>
+        <v>-0.385691</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>-0.465436</v>
+        <v>-0.88869</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.411668</v>
+        <v>0.942447</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.015818</v>
+        <v>0.34837</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.009276</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0.460412</v>
+        <v>0.45029</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>-0.031145</v>
+        <v>-0.014502</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>-0.057025</v>
+        <v>-0.075237</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0.054563</v>
+        <v>0.067984</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0.054563</v>
+        <v>0.067984</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0.001453</v>
+        <v>0.004271</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>-0.568704</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>-0.001813</v>
+        <v>0.585056</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>3.8e-05</v>
+        <v>-0.030518</v>
       </c>
       <c r="R101" s="3" t="n">
-        <v>-0.003766</v>
+        <v>-0.11178</v>
       </c>
     </row>
     <row r="102">
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.017805</v>
+        <v>-0.148588</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>-0.475163</v>
@@ -7095,13 +7095,13 @@
         <v>-1.67259</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>1.469074</v>
+        <v>1.999853</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.311634</v>
+        <v>0.644186</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.493432</v>
+        <v>0.502708</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>-1.237132</v>
@@ -7119,19 +7119,19 @@
         <v>-1.001766</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>-0.357127</v>
+        <v>-0.354309</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.712438</v>
+        <v>0.143734</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>-0.024703</v>
+        <v>0.5621660000000001</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>-0.229334</v>
+        <v>-0.25989</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>0.448947</v>
+        <v>0.340933</v>
       </c>
     </row>
     <row r="107">
@@ -7351,13 +7351,13 @@
         <v>0</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.008387</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.017915</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.027621</v>
       </c>
       <c r="Q110" s="3" t="n">
         <v>0</v>
@@ -7409,7 +7409,7 @@
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.076279</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>0</v>
@@ -7629,10 +7629,10 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.035625</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.072144</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
@@ -7641,10 +7641,10 @@
         <v>0</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.08164299999999999</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.183956</v>
       </c>
       <c r="P115" s="3" t="n">
         <v>0</v>
@@ -8793,7 +8793,7 @@
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.076279</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>0</v>
@@ -8861,7 +8861,7 @@
         </is>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-5.075806</v>
+        <v>-5.152085</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>-17.016154</v>
@@ -22811,7 +22811,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -23569,7 +23573,11 @@
           <t>Proceeds from Hatchet’s flow-through private placement</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -26359,7 +26367,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -26860,7 +26872,11 @@
           <t>Issuance of shares for private placement</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -26957,7 +26973,11 @@
           <t>Proceeds from Hatchet’s private placement</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -27458,7 +27478,11 @@
           <t>Loan payable applied to issuance of shares of private placement $</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -29472,7 +29496,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -30258,7 +30286,11 @@
           <t>Fair value of warrants issued on private placement $</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -31167,7 +31199,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -34314,7 +34350,11 @@
           <t>GST recoverable 4,767</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -37077,7 +37117,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -37970,7 +38014,11 @@
           <t>Proceeds from sale of marketable securities 3</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -49132,7 +49180,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>
@@ -58033,7 +58085,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
           <t>-</t>
@@ -60734,7 +60790,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E519" t="inlineStr">
         <is>
           <t>-</t>
@@ -62419,7 +62479,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E536" t="inlineStr">
         <is>
           <t>-</t>
@@ -64209,7 +64273,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr">
         <is>
           <t>-</t>
@@ -67003,7 +67071,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E582" t="inlineStr">
         <is>
           <t>-</t>
@@ -67710,7 +67782,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D589" t="inlineStr"/>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E589" t="inlineStr">
         <is>
           <t>-</t>
@@ -71007,7 +71083,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D622" t="inlineStr"/>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E622" s="5" t="n">
         <v>-0.130783</v>
       </c>
@@ -90984,7 +91064,11 @@
           <t>Future income tax recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D823" t="inlineStr"/>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E823" t="inlineStr">
         <is>
           <t>-</t>
@@ -94422,7 +94506,11 @@
           <t>Future income tax recovery (Note 11)</t>
         </is>
       </c>
-      <c r="D857" t="inlineStr"/>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E857" t="inlineStr">
         <is>
           <t>-</t>
